--- a/Archivio/Setup/NormalizzaInp.xlsx
+++ b/Archivio/Setup/NormalizzaInp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB46914-5C8D-4000-8418-252459B8D47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE82C4FA-ECA9-4AEA-8742-7DAF420CB3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="47">
   <si>
     <t>Azione</t>
   </si>
@@ -156,16 +156,16 @@
     <t>`Organization (OBS)`,`Providing Org#`,`Team (OBS)`,`Competence (Primary Value)`,`Job Location Region`</t>
   </si>
   <si>
-    <t>'01', LPAD(`Timesheet_Month`,2,0), `Timesheet_Year`</t>
-  </si>
-  <si>
     <t>`GEC`, LPAD(`Timesheet_Month`,2,0), `Timesheet_Year`</t>
   </si>
   <si>
-    <t>`Organization`,`Providing_Org`,`Team`,`Competence`,`Location_Region`</t>
-  </si>
-  <si>
     <t>`Short Name`,  LPAD(MONTH(`dateid`),2,0), YEAR(`dateid`)</t>
+  </si>
+  <si>
+    <t>`Org`,`Providing_Org`,`Team`,`Competence`,`Location_Region`</t>
+  </si>
+  <si>
+    <t>YEAR(`Timesheet_Date`), '-', LPAD(MONTH(`Timesheet_Date`),2,0), '-', '01'</t>
   </si>
 </sst>
 </file>
@@ -483,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -802,7 +802,7 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -842,7 +842,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -896,9 +896,12 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
         <v>22</v>
       </c>
       <c r="D22" t="s">
@@ -922,7 +925,7 @@
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -936,25 +939,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -962,10 +962,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -982,10 +985,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1002,13 +1005,13 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
@@ -1022,10 +1025,10 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -1042,10 +1045,10 @@
         <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -1062,13 +1065,13 @@
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s">
         <v>32</v>
@@ -1082,10 +1085,10 @@
         <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s">
         <v>30</v>
@@ -1099,19 +1102,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
         <v>32</v>
@@ -1125,16 +1125,16 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -1157,7 +1157,7 @@
         <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -1171,13 +1171,13 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
         <v>39</v>
@@ -1186,6 +1186,29 @@
         <v>32</v>
       </c>
       <c r="G35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Archivio/Setup/NormalizzaInp.xlsx
+++ b/Archivio/Setup/NormalizzaInp.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE82C4FA-ECA9-4AEA-8742-7DAF420CB3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79ECCE98-980F-4C00-9692-E913A667BDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Foglio 1'!$A$1:$G$37</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="48">
   <si>
     <t>Azione</t>
   </si>
@@ -93,24 +96,15 @@
     <t>Date</t>
   </si>
   <si>
-    <t>dateid</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
     <t>ADD</t>
   </si>
   <si>
-    <t>id_month_year</t>
-  </si>
-  <si>
     <t>nvarchar(50)</t>
   </si>
   <si>
-    <t>keyid</t>
-  </si>
-  <si>
     <t>nvarchar(100)</t>
   </si>
   <si>
@@ -126,9 +120,6 @@
     <t>pmo</t>
   </si>
   <si>
-    <t>KeyID</t>
-  </si>
-  <si>
     <t>KeyFTE_Mese</t>
   </si>
   <si>
@@ -166,6 +157,21 @@
   </si>
   <si>
     <t>YEAR(`Timesheet_Date`), '-', LPAD(MONTH(`Timesheet_Date`),2,0), '-', '01'</t>
+  </si>
+  <si>
+    <t>`Organization__OBS_`,`Providing_Org`,`Team__OBS_`,`Competence__Primary_Value_`,`Job_Location_Region`</t>
+  </si>
+  <si>
+    <t>`Short_Name`,  LPAD(MONTH(`dateid`),2,0), YEAR(`dateid`)</t>
+  </si>
+  <si>
+    <t>IdMonthYear</t>
+  </si>
+  <si>
+    <t>Keyid</t>
+  </si>
+  <si>
+    <t>Dateid</t>
   </si>
 </sst>
 </file>
@@ -483,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -679,10 +685,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -696,13 +702,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
         <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -716,13 +722,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -736,13 +742,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -756,13 +762,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -776,16 +782,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
         <v>22</v>
       </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -796,16 +805,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -816,16 +825,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
         <v>24</v>
       </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -836,16 +845,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -856,16 +865,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -876,16 +885,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
         <v>41</v>
       </c>
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
-      </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -896,19 +905,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -919,16 +925,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" t="s">
         <v>25</v>
       </c>
-      <c r="D23" t="s">
-        <v>28</v>
-      </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -939,16 +945,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -959,188 +965,182 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" t="s">
-        <v>26</v>
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" t="s">
         <v>28</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
       </c>
       <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
         <v>29</v>
       </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
       <c r="G28" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" t="s">
         <v>26</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>29</v>
       </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
         <v>24</v>
       </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" t="s">
         <v>28</v>
-      </c>
-      <c r="E30" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G31" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G32" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G33" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1148,22 +1148,22 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G34" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1171,22 +1171,22 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1194,25 +1194,53 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
         <v>35</v>
       </c>
-      <c r="D36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" t="s">
-        <v>39</v>
-      </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
         <v>31</v>
       </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G37" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:G32">
+      <sortCondition ref="B1:B37"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K0000FF Datalogic INTERNAL</oddFooter>

--- a/Archivio/Setup/NormalizzaInp.xlsx
+++ b/Archivio/Setup/NormalizzaInp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A27617-9E77-4F8B-8EE4-9458979CF850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D2B85E-6B2E-4441-AF9B-8116DFD5803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Foglio 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Foglio 1'!$A$1:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Foglio 1'!$A$1:$G$44</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="40">
   <si>
     <t>Azione</t>
   </si>
@@ -90,12 +90,6 @@
     <t>User Phone 2</t>
   </si>
   <si>
-    <t>REN</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
@@ -120,21 +114,6 @@
     <t>GEN</t>
   </si>
   <si>
-    <t>`Organization (OBS)`,`Providing Org#`,`Team (OBS)`,`Competence (Primary Value)`,`Job Location Region`</t>
-  </si>
-  <si>
-    <t>`GEC`, LPAD(`Timesheet_Month`,2,0), `Timesheet_Year`</t>
-  </si>
-  <si>
-    <t>`Short Name`,  LPAD(MONTH(`dateid`),2,0), YEAR(`dateid`)</t>
-  </si>
-  <si>
-    <t>`Org`,`Providing_Org`,`Team`,`Competence`,`Location_Region`</t>
-  </si>
-  <si>
-    <t>YEAR(`Timesheet_Date`), '-', LPAD(MONTH(`Timesheet_Date`),2,0), '-', '01'</t>
-  </si>
-  <si>
     <t>IdMonthYear</t>
   </si>
   <si>
@@ -168,13 +147,7 @@
     <t>nvarchar(100)</t>
   </si>
   <si>
-    <t>all_project_mapped_power_bi_column_set</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>INT UNSIGNED NOT NULL PRIMARY KEY AUTO_INCREMENT FIRST</t>
+    <t>`ShortName`,  LPAD(MONTH(`dateid`),2,0), YEAR(`dateid`)</t>
   </si>
 </sst>
 </file>
@@ -493,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
@@ -683,13 +656,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>22</v>
@@ -706,19 +676,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>9</v>
@@ -729,16 +696,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>9</v>
@@ -749,16 +716,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>9</v>
@@ -769,16 +736,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>9</v>
@@ -789,16 +756,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>9</v>
@@ -809,13 +776,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
@@ -829,13 +796,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>8</v>
@@ -849,16 +816,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>9</v>
@@ -869,16 +836,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -889,16 +856,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
@@ -909,16 +876,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>9</v>
@@ -929,474 +896,354 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>31</v>
+      <c r="D25" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>41</v>
+      <c r="D37" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/Archivio/Setup/NormalizzaInp.xlsx
+++ b/Archivio/Setup/NormalizzaInp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D2B85E-6B2E-4441-AF9B-8116DFD5803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE7AB14-F23A-4935-A3E6-9BF526A682AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio 1" sheetId="1" r:id="rId1"/>
@@ -63,33 +63,6 @@
     <t>EXL</t>
   </si>
   <si>
-    <t>Email Notifications Enabled</t>
-  </si>
-  <si>
-    <t>Network Authentication Name</t>
-  </si>
-  <si>
-    <t>RES Organization</t>
-  </si>
-  <si>
-    <t>RES Seniority</t>
-  </si>
-  <si>
-    <t>Skill (Primary Value)</t>
-  </si>
-  <si>
-    <t>Teams (Concatenated List)</t>
-  </si>
-  <si>
-    <t>Teams (Primary Value)</t>
-  </si>
-  <si>
-    <t>User Pager</t>
-  </si>
-  <si>
-    <t>User Phone 2</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
@@ -148,6 +121,33 @@
   </si>
   <si>
     <t>`ShortName`,  LPAD(MONTH(`dateid`),2,0), YEAR(`dateid`)</t>
+  </si>
+  <si>
+    <t>EmailNotificationsEnabled</t>
+  </si>
+  <si>
+    <t>NetworkAuthenticationName</t>
+  </si>
+  <si>
+    <t>RESOrganization</t>
+  </si>
+  <si>
+    <t>RESSeniority</t>
+  </si>
+  <si>
+    <t>SkillPrimaryValue</t>
+  </si>
+  <si>
+    <t>TeamsConcatenatedList</t>
+  </si>
+  <si>
+    <t>TeamsPrimaryValue</t>
+  </si>
+  <si>
+    <t>UserPager</t>
+  </si>
+  <si>
+    <t>UserPhone2</t>
   </si>
 </sst>
 </file>
@@ -506,7 +506,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -523,7 +523,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
@@ -557,7 +557,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
@@ -574,7 +574,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
@@ -608,7 +608,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -625,7 +625,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
@@ -642,7 +642,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
@@ -656,13 +656,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
@@ -676,13 +676,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
@@ -696,16 +696,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>9</v>
@@ -716,16 +716,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>9</v>
@@ -736,16 +736,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>9</v>
@@ -756,16 +756,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>9</v>
@@ -776,13 +776,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
@@ -796,13 +796,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>8</v>
@@ -816,16 +816,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>9</v>
@@ -836,16 +836,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -856,16 +856,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
@@ -876,16 +876,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>9</v>
@@ -896,82 +896,82 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -979,16 +979,16 @@
         <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -996,16 +996,16 @@
         <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1013,136 +1013,136 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1150,96 +1150,96 @@
         <v>7</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Archivio/Setup/NormalizzaInp.xlsx
+++ b/Archivio/Setup/NormalizzaInp.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE7AB14-F23A-4935-A3E6-9BF526A682AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91392AF-E32E-4DAD-8B8F-BE5F366DE589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Foglio 1'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Foglio 1'!$A$1:$G$39</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="38">
   <si>
     <t>Azione</t>
   </si>
@@ -109,12 +109,6 @@
   </si>
   <si>
     <t>`Org`,`ProvidingOrg`,`Team`,`Competence`,`LocationRegion`</t>
-  </si>
-  <si>
-    <t>pbx_key</t>
-  </si>
-  <si>
-    <t>`Org`,`SubOrg`,`Team`,`Competence`,`LocationRegion`</t>
   </si>
   <si>
     <t>nvarchar(100)</t>
@@ -466,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
@@ -506,7 +500,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -523,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
@@ -540,7 +534,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
@@ -557,7 +551,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
@@ -574,7 +568,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
@@ -591,7 +585,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
@@ -608,7 +602,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -625,7 +619,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
@@ -642,7 +636,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
@@ -682,7 +676,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
@@ -742,7 +736,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -782,7 +776,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
@@ -882,7 +876,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>15</v>
@@ -942,7 +936,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>8</v>
@@ -1113,7 +1107,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>14</v>
@@ -1145,105 +1139,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G39" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
